--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,498 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>135</v>
+      </c>
+      <c r="G2" t="n">
+        <v>135</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>135</v>
+      </c>
+      <c r="G3" t="n">
+        <v>135</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>155</v>
+      </c>
+      <c r="G5" t="n">
+        <v>155</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>155</v>
+      </c>
+      <c r="G6" t="n">
+        <v>155</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-L</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>條紋L</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HGI03024-100L</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>特大100L</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>195</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01022-WH-F</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美式復古渡假風純棉短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>白色F</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>650</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01021-ST-M</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>條紋M</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>650</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>67</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,457 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>平台</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HGI03023-GY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>奶霧灰</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>135</v>
-      </c>
-      <c r="G2" t="n">
-        <v>135</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>燕麥白</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>135</v>
-      </c>
-      <c r="G3" t="n">
-        <v>135</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>黑色</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>75</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>深藍XL</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>155</v>
-      </c>
-      <c r="G5" t="n">
-        <v>155</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HFA01022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HFA01022-WH-F</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>美式復古渡假風純棉短袖T恤</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>白色F</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>155</v>
-      </c>
-      <c r="G6" t="n">
-        <v>155</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HFA01022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HFA01022-BU-F</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>美式復古渡假風純棉短袖T恤</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>深海藍F</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>42</v>
-      </c>
-      <c r="G7" t="n">
-        <v>42</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HFA01020</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HFA01020-BGBK-F</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>翻領插肩袖寬鬆中長版短袖T恤</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>杏拼黑F</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>195</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HFA01021</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HFA01021-ST-M</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>美式復古寬鬆雲彩棉條紋短袖T恤</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>條紋M</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" t="n">
-        <v>65</v>
-      </c>
-      <c r="G9" t="n">
-        <v>650</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>深藍M</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>65</v>
-      </c>
-      <c r="G10" t="n">
-        <v>650</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>深藍M</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>67</v>
-      </c>
-      <c r="G11" t="n">
-        <v>67</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>深藍XL</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>67</v>
-      </c>
-      <c r="G12" t="n">
-        <v>67</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>露天</t>
         </is>
       </c>
     </row>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,498 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HGI03023-GY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>奶霧灰</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>135</v>
+      </c>
+      <c r="G2" t="n">
+        <v>135</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>135</v>
+      </c>
+      <c r="G3" t="n">
+        <v>135</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HGI03024-55L</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>大號55L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>155</v>
+      </c>
+      <c r="G5" t="n">
+        <v>155</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HGI03024-24L</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>小號24L</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>155</v>
+      </c>
+      <c r="G6" t="n">
+        <v>155</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HGI03022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HGI03022-WH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>新款PU皮立式化妝刷具旅行收納包</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>白蛋色</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>42</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>195</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>650</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>650</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HGI03024-40L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>中號40L</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HGI03024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HGI03024-66L</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天山棉麻衣物整理摺疊收納箱</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>加大66L</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>67</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,363 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HGI03023-WH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>燕麥白</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>135</v>
+      </c>
+      <c r="G2" t="n">
+        <v>135</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HGI03023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HGI03023-BK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M型短頸膚感防滑衣架</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>155</v>
+      </c>
+      <c r="G4" t="n">
+        <v>155</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-M</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>杏色M</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>155</v>
+      </c>
+      <c r="G5" t="n">
+        <v>155</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-XL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>深藍XL</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>195</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>650</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>官網</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HFA01019-DN-M</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>深藍M</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>67</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFA01019</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HFA01019-BG-XL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>厚磅撞色圓領短版修身短袖T恤</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>杏色XL</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>67</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,363 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>平台</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HGI03023-WH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>燕麥白</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>135</v>
-      </c>
-      <c r="G2" t="n">
-        <v>135</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HGI03023</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HGI03023-BK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>M型短頸膚感防滑衣架</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>黑色</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>75</v>
-      </c>
-      <c r="G3" t="n">
-        <v>75</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>杏色XL</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>155</v>
-      </c>
-      <c r="G4" t="n">
-        <v>155</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-M</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>杏色M</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>155</v>
-      </c>
-      <c r="G5" t="n">
-        <v>155</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-XL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>深藍XL</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>42</v>
-      </c>
-      <c r="G6" t="n">
-        <v>42</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>65</v>
-      </c>
-      <c r="G7" t="n">
-        <v>195</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>杏色XL</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>650</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>官網</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HFA01019-DN-M</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>深藍M</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>67</v>
-      </c>
-      <c r="G9" t="n">
-        <v>67</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>露天</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HFA01019</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HFA01019-BG-XL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>厚磅撞色圓領短版修身短袖T恤</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>杏色XL</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>67</v>
-      </c>
-      <c r="G10" t="n">
-        <v>67</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>露天</t>
         </is>
       </c>
     </row>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,48 +479,6 @@
           <t>匹配狀態</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HFF02001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HFF02001-SK-140G</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>裸感厚絨光腿褲襪</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>膚色140G</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>99</v>
-      </c>
-      <c r="G2" t="n">
-        <v>99</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>蝦皮</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/出庫.xlsx
+++ b/data/出庫.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,1186 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HFE03001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HFE03001-WH-L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>素色冰絲女士三角內褲</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>白色L</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HFA02001-TN-WH-L</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>【高領】白色L</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>155</v>
+      </c>
+      <c r="G3" t="n">
+        <v>155</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HFA02001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HFA02001-CN-WH-L</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>莫代爾長袖打底上衣</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>【圓領】白色L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>155</v>
+      </c>
+      <c r="G4" t="n">
+        <v>155</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HME03001-WH-XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>白色XL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>201</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HME03001-GY-XL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>灰色XL</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G6" t="n">
+        <v>67</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HME03001-PU-XL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>紫色XL</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>67</v>
+      </c>
+      <c r="G7" t="n">
+        <v>67</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HME03001-DN-XL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>藏藍色XL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>67</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HME03001-RD-XL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>酒紅色XL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>67</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HME03001-BR-XL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>咖啡色XL</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>67</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HME03001-PB-XL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>寶藍色XL</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67</v>
+      </c>
+      <c r="G11" t="n">
+        <v>67</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HME03001-BR-L</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>咖啡色L</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HME03001-WH-L</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>白色L</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>67</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>67</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>藏藍色L</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>67</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>寶藍色L</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>67</v>
+      </c>
+      <c r="G16" t="n">
+        <v>67</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HME03001-DN-M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>藏藍色M</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>201</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HME03001-GY-M</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>灰色M</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>201</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>201</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HME03001-PB-M</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>寶藍色M</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>67</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>268</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HME03001-PB-L</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>寶藍色L</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>67</v>
+      </c>
+      <c r="G22" t="n">
+        <v>268</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HME03001-BK-M</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>黑色M</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>67</v>
+      </c>
+      <c r="G23" t="n">
+        <v>335</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶加長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>134</v>
+      </c>
+      <c r="G24" t="n">
+        <v>134</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>夏天必備☀️莫代爾輕薄舒適無袖打底吊帶裙／背心裙｜三種長度｜寬肩帶細肩帶｜三色｜打底單穿｜襯裙｜台灣現貨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>【白色】吊帶款▶中長版 ❗️微透❗️::L</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>134</v>
+      </c>
+      <c r="G25" t="n">
+        <v>134</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HME03001-BK-L</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>黑色L</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>67</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HME03001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HME03001-DN-L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>超薄裸感冰絲男士四角內褲</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>藏藍色L</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>67</v>
+      </c>
+      <c r="G27" t="n">
+        <v>67</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>已匹配</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>露天</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
